--- a/reports/FV_Assets_Details_2026.xlsx
+++ b/reports/FV_Assets_Details_2026.xlsx
@@ -13,7 +13,18 @@
     <sheet name="FV Store Inventory" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="FV Assets Summery" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'FV Washroom Details'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'FV Washroom Details'!$A$1:$I$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FV Handicap Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'FV Handicap Washroom'!$A$1:$H$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'FV Baby Room'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'FV Baby Room'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'FV Store Inventory'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'FV Store Inventory'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'FV Assets Summery'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'FV Assets Summery'!$A$1:$H$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -548,7 +559,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1377,6 +1388,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1384,7 +1396,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2078,6 +2090,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2085,7 +2098,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2687,6 +2700,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2694,7 +2708,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2784,6 +2798,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2791,7 +2806,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2896,5 +2911,6 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/reports/FV_Assets_Details_2026.xlsx
+++ b/reports/FV_Assets_Details_2026.xlsx
@@ -12,6 +12,16 @@
     <sheet name="FV Baby Room" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="FV Store Inventory" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="FV Assets Summery" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FV Washroom (Detailed)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="FV Handicap (Detailed)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="FV Baby Room (Detailed)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FV Prayer Room" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="FV Common Area Bins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="FV Seating Area New" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="FV Seating Area Old" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="FV Assets" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="FV Planter Pots" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="FV Photo Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FV Washroom Details'!$1:$2</definedName>
@@ -24,6 +34,26 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'FV Store Inventory'!$A$1:$E$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'FV Assets Summery'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'FV Assets Summery'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'FV Washroom (Detailed)'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'FV Washroom (Detailed)'!$A$1:$Y$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'FV Handicap (Detailed)'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'FV Handicap (Detailed)'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'FV Baby Room (Detailed)'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'FV Baby Room (Detailed)'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'FV Prayer Room'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'FV Prayer Room'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'FV Common Area Bins'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'FV Common Area Bins'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'FV Seating Area New'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'FV Seating Area New'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'FV Seating Area Old'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'FV Seating Area Old'!$A$1:$K$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'FV Assets'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'FV Assets'!$A$1:$E$43</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'FV Planter Pots'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'FV Planter Pots'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'FV Photo Reference'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'FV Photo Reference'!$A$1:$D$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +62,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +103,24 @@
       <color rgb="00000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -92,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -168,11 +216,23 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -194,6 +254,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -270,6 +343,1917 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1123950" cy="904875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>22</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1123950" cy="904875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1123950" cy="904875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1123950" cy="904875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1123950" cy="904875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1123950" cy="904875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>19050</colOff>
+      <row>2</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>19050</colOff>
+      <row>3</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>666750</colOff>
+      <row>3</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>1314450</colOff>
+      <row>3</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>19050</colOff>
+      <row>5</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>666750</colOff>
+      <row>5</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>19050</colOff>
+      <row>4</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>19050</colOff>
+      <row>2</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>19050</colOff>
+      <row>5</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>666750</colOff>
+      <row>2</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>19050</colOff>
+      <row>4</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="609600" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1143000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1381125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1381125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1381125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1381125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1381125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <ext cx="1219200" cy="1381125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1392,6 +3376,1789 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28.45" customWidth="1" min="1" max="1"/>
+    <col width="18.45" customWidth="1" min="2" max="2"/>
+    <col width="28.45" customWidth="1" min="3" max="3"/>
+    <col width="18.45" customWidth="1" min="4" max="4"/>
+    <col width="24.45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.4" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Round Bins</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sub Location</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total </t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="37.4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Parking level 2</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Parking level 3</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Parking level 4</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Parking level 5</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Parking Level 6</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Tower 1</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>GF waitrose area</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Tower 1</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Mezanine Floor</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Tower 2</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>GF Food hall</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tower 1 </t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>P1 Level</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Tower 4</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Mezanine Floor</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Tower 4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Tower 2</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>P1 Level</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Link Bridge</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>From TDM - P1</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Total Floor</t>
+        </is>
+      </c>
+      <c r="B16" s="14">
+        <f>SUM(B3:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14">
+        <f>SUM(B16:B16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.45" customWidth="1" min="1" max="1"/>
+    <col width="34.45" customWidth="1" min="2" max="2"/>
+    <col width="22.45" customWidth="1" min="3" max="3"/>
+    <col width="18.45" customWidth="1" min="4" max="4"/>
+    <col width="18.45" customWidth="1" min="5" max="5"/>
+    <col width="18.45" customWidth="1" min="6" max="6"/>
+    <col width="18.45" customWidth="1" min="7" max="7"/>
+    <col width="18.45" customWidth="1" min="8" max="8"/>
+    <col width="18.45" customWidth="1" min="9" max="9"/>
+    <col width="18.45" customWidth="1" min="10" max="10"/>
+    <col width="18.45" customWidth="1" min="11" max="11"/>
+    <col width="26.45" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.4" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Location &amp; Description</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Pictures</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carpet </t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Round Sofas</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Long benches</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curved Sofas </t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Chairs</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planters </t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="37.4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="99.95" customHeight="1">
+      <c r="A3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>L1 Tower-2 area</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Active on Floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="99.95" customHeight="1">
+      <c r="A4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mezzanine Floor area </t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed </t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="99.95" customHeight="1">
+      <c r="A5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>FV link bridge</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Active on Floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="99.95" customHeight="1">
+      <c r="A6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grand floor waitrose sitting area </t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Active on Floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="99.95" customHeight="1">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14">
+        <f>SUBTOTAL(9,D3:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="14">
+        <f>SUBTOTAL(9,E3:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="14">
+        <f>SUBTOTAL(9,F3:F6)</f>
+        <v/>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="14">
+        <f>SUBTOTAL(9,H3:H6)</f>
+        <v/>
+      </c>
+      <c r="I7" s="14">
+        <f>SUBTOTAL(9,I3:I6)</f>
+        <v/>
+      </c>
+      <c r="J7" s="14">
+        <f>SUBTOTAL(9,J3:J6)</f>
+        <v/>
+      </c>
+      <c r="K7" s="14">
+        <f>SUBTOTAL(9,K3:K6)</f>
+        <v/>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>Active on Floor</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.45" customWidth="1" min="1" max="1"/>
+    <col width="34.45" customWidth="1" min="2" max="2"/>
+    <col width="22.45" customWidth="1" min="3" max="3"/>
+    <col width="18.45" customWidth="1" min="4" max="4"/>
+    <col width="18.45" customWidth="1" min="5" max="5"/>
+    <col width="18.45" customWidth="1" min="6" max="6"/>
+    <col width="18.45" customWidth="1" min="7" max="7"/>
+    <col width="18.45" customWidth="1" min="8" max="8"/>
+    <col width="18.45" customWidth="1" min="9" max="9"/>
+    <col width="18.45" customWidth="1" min="10" max="10"/>
+    <col width="26.45" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.4" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Location &amp; Description</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Pictures</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carpet </t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Round Sofas</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brown mall Sofas </t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Chairs</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Square mall Tables</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planters </t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="37.4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="99.95" customHeight="1">
+      <c r="A3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>L1 Tower-2 area</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="99.95" customHeight="1">
+      <c r="A4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mezzanine Floor area </t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="99.95" customHeight="1">
+      <c r="A5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ground floor waitrose sitting area </t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="99.95" customHeight="1">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="99.95" customHeight="1">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14">
+        <f>SUBTOTAL(9,D3:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="14">
+        <f>SUBTOTAL(9,E3:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="14">
+        <f>SUBTOTAL(9,F3:F6)</f>
+        <v/>
+      </c>
+      <c r="G7" s="14">
+        <f>SUBTOTAL(9,G3:G6)</f>
+        <v/>
+      </c>
+      <c r="H7" s="14">
+        <f>SUBTOTAL(9,H3:H6)</f>
+        <v/>
+      </c>
+      <c r="I7" s="14">
+        <f>SUBTOTAL(9,I3:I6)</f>
+        <v/>
+      </c>
+      <c r="J7" s="14">
+        <f>SUBTOTAL(9,J3:J6)</f>
+        <v/>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>Active on Floor</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.45" customWidth="1" min="1" max="1"/>
+    <col width="22.45" customWidth="1" min="2" max="2"/>
+    <col width="40.45" customWidth="1" min="3" max="3"/>
+    <col width="18.45" customWidth="1" min="4" max="4"/>
+    <col width="24.45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.4" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Quantity on Floor</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="37.4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="109.5" customHeight="1">
+      <c r="A3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Big planters pots </t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="109.5" customHeight="1">
+      <c r="A4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium planters pots </t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="109.5" customHeight="1">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Black planters Pot</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="109.5" customHeight="1">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Small Gray pot</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="109.5" customHeight="1">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Big Gray Pot</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="109.5" customHeight="1">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">medium Gray planters pots </t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="109.5" customHeight="1">
+      <c r="A9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common area Bins </t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="109.5" customHeight="1">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">External parking bins </t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="109.5" customHeight="1">
+      <c r="A11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Food court bins station </t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="109.5" customHeight="1">
+      <c r="A12" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt White Single Chair</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="109.5" customHeight="1">
+      <c r="A13" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Wooden Single Chair</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="109.5" customHeight="1">
+      <c r="A14" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Round White Table</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="109.5" customHeight="1">
+      <c r="A15" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Cream Single Chair</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="109.5" customHeight="1">
+      <c r="A16" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Square White Table</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="109.5" customHeight="1">
+      <c r="A17" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Long Table</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="109.5" customHeight="1">
+      <c r="A18" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Gray 2 seater Sofa</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="109.5" customHeight="1">
+      <c r="A19" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Black Single Chair</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="109.5" customHeight="1">
+      <c r="A20" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Square Black Table</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="109.5" customHeight="1">
+      <c r="A21" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Black Wooden Single Chair</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="109.5" customHeight="1">
+      <c r="A22" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Round Gray Table</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="109.5" customHeight="1">
+      <c r="A23" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Round Green Table</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="109.5" customHeight="1">
+      <c r="A24" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Foodcourt Orange Single Chair</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="109.5" customHeight="1">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Green steel chairs with back rest and arms </t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="109.5" customHeight="1">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="109.5" customHeight="1">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="109.5" customHeight="1">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Donut Seats</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="109.5" customHeight="1">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Gray Long Sofa</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="109.5" customHeight="1">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Big Pink Hexagon Shape Sofa</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="109.5" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Small Pink Hexagon Shape Sofa</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="109.5" customHeight="1">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Small Gray Hexagon Shape Sofa</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="109.5" customHeight="1">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Blue Single Sofa</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="109.5" customHeight="1">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Gray Single Sofa</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="109.5" customHeight="1">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Pink Single Sofa</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="109.5" customHeight="1">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Round Gray Coffee Table</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="109.5" customHeight="1">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Round White Coffee Table</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="109.5" customHeight="1">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="109.5" customHeight="1">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two seater leather sofas </t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="109.5" customHeight="1">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">two seater fabric sofas </t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="109.5" customHeight="1">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>White small</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="109.5" customHeight="1">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Linkbridge new plant white</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="10" t="n"/>
+    </row>
+    <row r="43" ht="109.5" customHeight="1">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Linkbridge new bamboo plant white</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.45" customWidth="1" min="1" max="1"/>
+    <col width="22.45" customWidth="1" min="2" max="2"/>
+    <col width="40.45" customWidth="1" min="3" max="3"/>
+    <col width="18.45" customWidth="1" min="4" max="4"/>
+    <col width="24.45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.4" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Quantity on Floor</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="37.4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="109.5" customHeight="1">
+      <c r="A3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Big planters pots </t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="109.5" customHeight="1">
+      <c r="A4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium planters pots </t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="109.5" customHeight="1">
+      <c r="A5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Black planters Pot</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="109.5" customHeight="1">
+      <c r="A6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Small Gray pot</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="109.5" customHeight="1">
+      <c r="A7" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Big Gray Pot</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="109.5" customHeight="1">
+      <c r="A8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">medium Gray planters pots </t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="109.5" customHeight="1">
+      <c r="A9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>White small</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="109.5" customHeight="1">
+      <c r="A10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Linkbridge new plant white</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="109.5" customHeight="1">
+      <c r="A11" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Linkbridge new bamboo plant white</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28.45" customWidth="1" min="1" max="1"/>
+    <col width="18.45" customWidth="1" min="2" max="2"/>
+    <col width="22.45" customWidth="1" min="3" max="3"/>
+    <col width="24.45" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.4" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Source tab</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Shown at</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="37.4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="115" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>FV Washroom (Detailed)</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>AA3</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="115" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>FV Washroom (Detailed)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="115" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>FV Handicap (Detailed)</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="115" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>FV Baby Room (Detailed)</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="115" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>FV Prayer Room</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="115" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>FV Common Area Bins</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2913,4 +6680,4445 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Y27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30.45" customWidth="1" min="1" max="1"/>
+    <col width="14.45" customWidth="1" min="2" max="2"/>
+    <col width="20.45" customWidth="1" min="3" max="3"/>
+    <col width="18.45" customWidth="1" min="4" max="4"/>
+    <col width="18.45" customWidth="1" min="5" max="5"/>
+    <col width="18.45" customWidth="1" min="6" max="6"/>
+    <col width="18.45" customWidth="1" min="7" max="7"/>
+    <col width="18.45" customWidth="1" min="8" max="8"/>
+    <col width="18.45" customWidth="1" min="9" max="9"/>
+    <col width="18.45" customWidth="1" min="10" max="10"/>
+    <col width="18.45" customWidth="1" min="11" max="11"/>
+    <col width="18.45" customWidth="1" min="12" max="12"/>
+    <col width="18.45" customWidth="1" min="13" max="13"/>
+    <col width="18.45" customWidth="1" min="14" max="14"/>
+    <col width="18.45" customWidth="1" min="15" max="15"/>
+    <col width="18.45" customWidth="1" min="16" max="16"/>
+    <col width="18.45" customWidth="1" min="17" max="17"/>
+    <col width="18.45" customWidth="1" min="18" max="18"/>
+    <col width="18.45" customWidth="1" min="19" max="19"/>
+    <col width="18.45" customWidth="1" min="20" max="20"/>
+    <col width="18.45" customWidth="1" min="21" max="21"/>
+    <col width="18.45" customWidth="1" min="22" max="22"/>
+    <col width="18.45" customWidth="1" min="23" max="23"/>
+    <col width="18.45" customWidth="1" min="24" max="24"/>
+    <col width="26.45" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.4" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Washroom no</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Washroom (Gender)</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Cubicle</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>WC Flexible Hose Pipe</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Toilet roll dispenser-1</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Toilet roll dispenser-2</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coat Hook </t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>Cubicle pedal bins</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand  Towel Dispenser </t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wall Mounted tissue Dispenser </t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>Urinal</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
+          <t>Urinal Side glass</t>
+        </is>
+      </c>
+      <c r="N1" s="11" t="inlineStr">
+        <is>
+          <t>Wall mirror</t>
+        </is>
+      </c>
+      <c r="O1" s="11" t="inlineStr">
+        <is>
+          <t>Vanity mirror</t>
+        </is>
+      </c>
+      <c r="P1" s="11" t="inlineStr">
+        <is>
+          <t>Wash basin</t>
+        </is>
+      </c>
+      <c r="Q1" s="11" t="inlineStr">
+        <is>
+          <t>Washbasin Taps</t>
+        </is>
+      </c>
+      <c r="R1" s="11" t="inlineStr">
+        <is>
+          <t>Soap Tap</t>
+        </is>
+      </c>
+      <c r="S1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand Dryer </t>
+        </is>
+      </c>
+      <c r="T1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cubicle Photo Frame </t>
+        </is>
+      </c>
+      <c r="U1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wall Entrance photo Frame </t>
+        </is>
+      </c>
+      <c r="V1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fabric Couch </t>
+        </is>
+      </c>
+      <c r="W1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fabric Round couch  </t>
+        </is>
+      </c>
+      <c r="X1" s="11" t="inlineStr">
+        <is>
+          <t>Janitor room Wash basin with Tap</t>
+        </is>
+      </c>
+      <c r="Y1" s="9" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="107.5" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="12" t="n"/>
+      <c r="N2" s="12" t="n"/>
+      <c r="O2" s="12" t="n"/>
+      <c r="P2" s="12" t="n"/>
+      <c r="Q2" s="12" t="n"/>
+      <c r="R2" s="12" t="n"/>
+      <c r="S2" s="12" t="n"/>
+      <c r="T2" s="12" t="n"/>
+      <c r="U2" s="12" t="n"/>
+      <c r="V2" s="12" t="n"/>
+      <c r="W2" s="12" t="n"/>
+      <c r="X2" s="12" t="n"/>
+      <c r="Y2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="20.15" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>GF - Tower 1</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="20.15" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="20.15" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>LGM - Tower 1</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="10" t="n"/>
+      <c r="W5" s="10" t="n"/>
+      <c r="X5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="20.15" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="10" t="n"/>
+      <c r="W6" s="10" t="n"/>
+      <c r="X6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="20.15" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>P1- Tower 1</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="10" t="n"/>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="20.15" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R8" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="10" t="n"/>
+      <c r="W8" s="10" t="n"/>
+      <c r="X8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="20.15" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1- Tower 1 -PR Side </t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="10" t="n"/>
+      <c r="W9" s="10" t="n"/>
+      <c r="X9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="20.15" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="10" t="n"/>
+      <c r="W10" s="10" t="n"/>
+      <c r="X10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="20.15" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GF-Link Bridge -Food court</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S11" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="10" t="n"/>
+      <c r="W11" s="10" t="n"/>
+      <c r="X11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="20.15" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="20.15" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> LGM-Link Bridge -Food court</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="10" t="n"/>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="20.15" customHeight="1">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="10" t="n"/>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="20.15" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> P1-Link Bridge -Food court</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R15" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U15" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V15" s="10" t="n"/>
+      <c r="W15" s="10" t="n"/>
+      <c r="X15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="20.15" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U16" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="20.15" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GF -Tower 2 Food court </t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="10" t="n"/>
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="10" t="n"/>
+      <c r="Y17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="20.15" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="20.15" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LGM -Tower 2 Food court </t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="10" t="n"/>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="10" t="n"/>
+      <c r="Y19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="20.15" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="10" t="n"/>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="10" t="n"/>
+      <c r="O20" s="10" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="10" t="n"/>
+      <c r="R20" s="10" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
+      <c r="U20" s="10" t="n"/>
+      <c r="V20" s="10" t="n"/>
+      <c r="W20" s="10" t="n"/>
+      <c r="X20" s="10" t="n"/>
+      <c r="Y20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="20.15" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1-Tower 2 Food court </t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="10" t="n"/>
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="20.15" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q22" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="S22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="10" t="n"/>
+      <c r="W22" s="10" t="n"/>
+      <c r="X22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="20.15" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GF - Link bridge -Food court Staff </t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="10" t="n"/>
+      <c r="W23" s="10" t="n"/>
+      <c r="X23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="20.15" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="10" t="n"/>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="20.15" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total </t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D25" s="14">
+        <f>SUM(D3+D5+D7+D9+D11+D13+D15+D17+D19+D21+D23)</f>
+        <v/>
+      </c>
+      <c r="E25" s="14">
+        <f>SUM(E3+E5+E7+E9+E11+E13+E15+E17+E19+E21+E23)</f>
+        <v/>
+      </c>
+      <c r="F25" s="14">
+        <f>SUM(F3+F5+F7+F9+F11+F13+F15+F17+F19+F21+F23)</f>
+        <v/>
+      </c>
+      <c r="G25" s="14">
+        <f>SUM(G3+G5+G7+G9+G11+G13+G15+G17+G19+G21+G23)</f>
+        <v/>
+      </c>
+      <c r="H25" s="14">
+        <f>SUM(H3+H5+H7+H9+H11+H13+H15+H17+H19+H21+H23)</f>
+        <v/>
+      </c>
+      <c r="I25" s="14">
+        <f>SUM(I3+I5+I7+I9+I11+I13+I15+I17+I19+I21+I23)</f>
+        <v/>
+      </c>
+      <c r="J25" s="14">
+        <f>SUM(J3+J5+J7+J9+J11+J13+J15+J17+J19+J21+J23)</f>
+        <v/>
+      </c>
+      <c r="K25" s="14">
+        <f>SUM(K3+K5+K7+K9+K11+K13+K15+K17+K19+K21+K23)</f>
+        <v/>
+      </c>
+      <c r="L25" s="14">
+        <f>SUM(L3+L5+L7+L9+L11+L13+L15+L17+L19+L21+L23)</f>
+        <v/>
+      </c>
+      <c r="M25" s="14">
+        <f>SUM(M3+M5+M7+M9+M11+M13+M15+M17+M19+M21+M23)</f>
+        <v/>
+      </c>
+      <c r="N25" s="14">
+        <f>SUM(N3+N5+N7+N9+N11+N13+N15+N17+N19+N21+N23)</f>
+        <v/>
+      </c>
+      <c r="O25" s="14">
+        <f>SUM(O3+O5+O7+O9+O11+O13+O15+O17+O19+O21+O23)</f>
+        <v/>
+      </c>
+      <c r="P25" s="14">
+        <f>SUM(P3+P5+P7+P9+P11+P13+P15+P17+P19+P21+P23)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="14">
+        <f>SUM(Q3+Q5+Q7+Q9+Q11+Q13+Q15+Q17+Q19+Q21+Q23)</f>
+        <v/>
+      </c>
+      <c r="R25" s="14">
+        <f>SUM(R3+R5+R7+R9+R11+R13+R15+R17+R19+R21+R23)</f>
+        <v/>
+      </c>
+      <c r="S25" s="14">
+        <f>SUM(S3+S5+S7+S9+S11+S13+S15+S17+S19+S21+S23)</f>
+        <v/>
+      </c>
+      <c r="T25" s="14">
+        <f>SUM(T3+T5+T7+T9+T11+T13+T15+T17+T19+T21+T23)</f>
+        <v/>
+      </c>
+      <c r="U25" s="14">
+        <f>SUM(U3+U5+U7+U9+U11+U13+U15+U17+U19+U21+U23)</f>
+        <v/>
+      </c>
+      <c r="V25" s="14" t="n"/>
+      <c r="W25" s="14" t="n"/>
+      <c r="X25" s="14">
+        <f>SUM(X3+X5+X7+X9+X11+X13+X15+X17+X19+X21+X23)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="20.15" customHeight="1">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D26" s="14">
+        <f>SUM(D4+D6+D8+D10+D12+D14+D16+D18+D20+D22+D24)</f>
+        <v/>
+      </c>
+      <c r="E26" s="14">
+        <f>SUM(E4+E6+E8+E10+E12+E14+E16+E18+E20+E22+E24)</f>
+        <v/>
+      </c>
+      <c r="F26" s="14">
+        <f>SUM(F4+F6+F8+F10+F12+F14+F16+F18+F20+F22+F24)</f>
+        <v/>
+      </c>
+      <c r="G26" s="14">
+        <f>SUM(G4+G6+G8+G10+G12+G14+G16+G18+G20+G22+G24)</f>
+        <v/>
+      </c>
+      <c r="H26" s="14">
+        <f>SUM(H4+H6+H8+H10+H12+H14+H16+H18+H20+H22+H24)</f>
+        <v/>
+      </c>
+      <c r="I26" s="14">
+        <f>SUM(I4+I6+I8+I10+I12+I14+I16+I18+I20+I22+I24)</f>
+        <v/>
+      </c>
+      <c r="J26" s="14">
+        <f>SUM(J4+J6+J8+J10+J12+J14+J16+J18+J20+J22+J24)</f>
+        <v/>
+      </c>
+      <c r="K26" s="14">
+        <f>SUM(K4+K6+K8+K10+K12+K14+K16+K18+K20+K22+K24)</f>
+        <v/>
+      </c>
+      <c r="L26" s="14">
+        <f>SUM(L4+L6+L8+L10+L12+L14+L16+L18+L20+L22+L24)</f>
+        <v/>
+      </c>
+      <c r="M26" s="14">
+        <f>SUM(M4+M6+M8+M10+M12+M14+M16+M18+M20+M22+M24)</f>
+        <v/>
+      </c>
+      <c r="N26" s="14">
+        <f>SUM(N4+N6+N8+N10+N12+N14+N16+N18+N20+N22+N24)</f>
+        <v/>
+      </c>
+      <c r="O26" s="14">
+        <f>SUM(O4+O6+O8+O10+O12+O14+O16+O18+O20+O22+O24)</f>
+        <v/>
+      </c>
+      <c r="P26" s="14">
+        <f>SUM(P4+P6+P8+P10+P12+P14+P16+P18+P20+P22+P24)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="14">
+        <f>SUM(Q4+Q6+Q8+Q10+Q12+Q14+Q16+Q18+Q20+Q22+Q24)</f>
+        <v/>
+      </c>
+      <c r="R26" s="14">
+        <f>SUM(R4+R6+R8+R10+R12+R14+R16+R18+R20+R22+R24)</f>
+        <v/>
+      </c>
+      <c r="S26" s="14">
+        <f>SUM(S4+S6+S8+S10+S12+S14+S16+S18+S20+S22+S24)</f>
+        <v/>
+      </c>
+      <c r="T26" s="14">
+        <f>SUM(T4+T6+T8+T10+T12+T14+T16+T18+T20+T22+T24)</f>
+        <v/>
+      </c>
+      <c r="U26" s="14">
+        <f>SUM(U4+U6+U8+U10+U12+U14+U16+U18+U20+U22+U24)</f>
+        <v/>
+      </c>
+      <c r="V26" s="14" t="n"/>
+      <c r="W26" s="14" t="n"/>
+      <c r="X26" s="14">
+        <f>SUM(X4+X6+X8+X10+X12+X14+X16+X18+X20+X22+X24)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="14" t="n"/>
+    </row>
+    <row r="27" ht="20.15" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal </t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14">
+        <f>SUM(D25+D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="14">
+        <f>SUM(E25+E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="14">
+        <f>SUM(F25+F26)</f>
+        <v/>
+      </c>
+      <c r="G27" s="14">
+        <f>SUM(G25+G26)</f>
+        <v/>
+      </c>
+      <c r="H27" s="14">
+        <f>SUM(H25+H26)</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>SUM(I25+I26)</f>
+        <v/>
+      </c>
+      <c r="J27" s="14">
+        <f>SUM(J25+J26)</f>
+        <v/>
+      </c>
+      <c r="K27" s="14">
+        <f>SUM(K25+K26)</f>
+        <v/>
+      </c>
+      <c r="L27" s="14">
+        <f>SUM(L25+L26)</f>
+        <v/>
+      </c>
+      <c r="M27" s="14">
+        <f>SUM(M25+M26)</f>
+        <v/>
+      </c>
+      <c r="N27" s="14">
+        <f>SUM(N25+N26)</f>
+        <v/>
+      </c>
+      <c r="O27" s="14">
+        <f>SUM(O25+O26)</f>
+        <v/>
+      </c>
+      <c r="P27" s="14">
+        <f>SUM(P25+P26)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="14">
+        <f>SUM(Q25+Q26)</f>
+        <v/>
+      </c>
+      <c r="R27" s="14">
+        <f>SUM(R25+R26)</f>
+        <v/>
+      </c>
+      <c r="S27" s="14">
+        <f>SUM(S25+S26)</f>
+        <v/>
+      </c>
+      <c r="T27" s="14">
+        <f>SUM(T25+T26)</f>
+        <v/>
+      </c>
+      <c r="U27" s="14">
+        <f>SUM(U25+U26)</f>
+        <v/>
+      </c>
+      <c r="V27" s="14" t="n"/>
+      <c r="W27" s="14" t="n"/>
+      <c r="X27" s="14">
+        <f>SUM(X25+X26)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30.45" customWidth="1" min="1" max="1"/>
+    <col width="14.45" customWidth="1" min="2" max="2"/>
+    <col width="20.45" customWidth="1" min="3" max="3"/>
+    <col width="18.45" customWidth="1" min="4" max="4"/>
+    <col width="18.45" customWidth="1" min="5" max="5"/>
+    <col width="18.45" customWidth="1" min="6" max="6"/>
+    <col width="18.45" customWidth="1" min="7" max="7"/>
+    <col width="18.45" customWidth="1" min="8" max="8"/>
+    <col width="18.45" customWidth="1" min="9" max="9"/>
+    <col width="18.45" customWidth="1" min="10" max="10"/>
+    <col width="18.45" customWidth="1" min="11" max="11"/>
+    <col width="18.45" customWidth="1" min="12" max="12"/>
+    <col width="18.45" customWidth="1" min="13" max="13"/>
+    <col width="18.45" customWidth="1" min="14" max="14"/>
+    <col width="26.45" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.4" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Washroom no</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Washroom (Gender)</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Cubicle</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>WC Flexible Hose Pipe</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Toilet roll dispenser</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Cubicle pedal bins</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand dryer </t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>Vanity mirror</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>Wash basin</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>Washbasin Taps</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soap Dispenser </t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coat Hook </t>
+        </is>
+      </c>
+      <c r="N1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand Tissue </t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="107.5" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="12" t="n"/>
+      <c r="N2" s="12" t="n"/>
+      <c r="O2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="20.15" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>GF - Tower 1</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="20.15" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="20.15" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>LGM - Tower 1</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="20.15" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="20.15" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>P1- Tower 1</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="20.15" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="20.15" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1- Tower 1 -PR Side </t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="20.15" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="20.15" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GF-Link Bridge -Food court</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="20.15" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="20.15" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> LGM-Link Bridge -Food court</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="20.15" customHeight="1">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="20.15" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> P1-Link Bridge -Food court</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="20.15" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="20.15" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GF -Tower 2 Food court </t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="20.15" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="20.15" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LGM -Tower 2 Food court </t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="20.15" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="10" t="n"/>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="10" t="n"/>
+      <c r="O20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="20.15" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1-Tower 2 Food court </t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="20.15" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="20.15" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total </t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D23" s="14">
+        <f>SUM(D3+D5+D7+D9+D11+D13+D15+D17+D19+D21)</f>
+        <v/>
+      </c>
+      <c r="E23" s="14">
+        <f>SUM(E3+E5+E7+E9+E11+E13+E15+E17+E19+E21)</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>SUM(F3+F5+F7+F9+F11+F13+F15+F17+F19+F21)</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>SUM(G3+G5+G7+G9+G11+G13+G15+G17+G19+G21)</f>
+        <v/>
+      </c>
+      <c r="H23" s="14">
+        <f>SUM(H3+H5+H7+H9+H11+H13+H15+H17+H19+H21)</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>SUM(I3+I5+I7+I9+I11+I13+I15+I17+I19+I21)</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>SUM(J3+J5+J7+J9+J11+J13+J15+J17+J19+J21)</f>
+        <v/>
+      </c>
+      <c r="K23" s="14">
+        <f>SUM(K3+K5+K7+K9+K11+K13+K15+K17+K19+K21)</f>
+        <v/>
+      </c>
+      <c r="L23" s="14">
+        <f>SUM(L3+L5+L7+L9+L11+L13+L15+L17+L19+L21)</f>
+        <v/>
+      </c>
+      <c r="M23" s="14">
+        <f>SUM(M3+M5+M7+M9+M11+M13+M15+M17+M19+M21)</f>
+        <v/>
+      </c>
+      <c r="N23" s="14">
+        <f>SUM(N3+N5+N7+N9+N11+N13+N15+N17+N19+N21)</f>
+        <v/>
+      </c>
+      <c r="O23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="20.15" customHeight="1">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D24" s="14">
+        <f>SUM(D4+D6+D8+D10+D12+D14+D16+D18+D20+D22)</f>
+        <v/>
+      </c>
+      <c r="E24" s="14">
+        <f>SUM(E4+E6+E8+E10+E12+E14+E16+E18+E20+E22)</f>
+        <v/>
+      </c>
+      <c r="F24" s="14">
+        <f>SUM(F4+F6+F8+F10+F12+F14+F16+F18+F20+F22)</f>
+        <v/>
+      </c>
+      <c r="G24" s="14">
+        <f>SUM(G4+G6+G8+G10+G12+G14+G16+G18+G20+G22)</f>
+        <v/>
+      </c>
+      <c r="H24" s="14">
+        <f>SUM(H4+H6+H8+H10+H12+H14+H16+H18+H20+H22)</f>
+        <v/>
+      </c>
+      <c r="I24" s="14">
+        <f>SUM(I4+I6+I8+I10+I12+I14+I16+I18+I20+I22)</f>
+        <v/>
+      </c>
+      <c r="J24" s="14">
+        <f>SUM(J4+J6+J8+J10+J12+J14+J16+J18+J20+J22)</f>
+        <v/>
+      </c>
+      <c r="K24" s="14">
+        <f>SUM(K4+K6+K8+K10+K12+K14+K16+K18+K20+K22)</f>
+        <v/>
+      </c>
+      <c r="L24" s="14">
+        <f>SUM(L4+L6+L8+L10+L12+L14+L16+L18+L20+L22)</f>
+        <v/>
+      </c>
+      <c r="M24" s="14">
+        <f>SUM(M4+M6+M8+M10+M12+M14+M16+M18+M20+M22)</f>
+        <v/>
+      </c>
+      <c r="N24" s="14">
+        <f>SUM(N4+N6+N8+N10+N12+N14+N16+N18+N20+N22)</f>
+        <v/>
+      </c>
+      <c r="O24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="20.15" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal </t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14">
+        <f>SUM(D23+D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="14">
+        <f>SUM(E23+E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="14">
+        <f>SUM(F23+F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="14">
+        <f>SUM(G23+G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="14">
+        <f>SUM(H23+H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="14">
+        <f>SUM(I23+I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="14">
+        <f>SUM(J23+J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="14">
+        <f>SUM(K23+K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="14">
+        <f>SUM(L23+L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="14">
+        <f>SUM(M23+M24)</f>
+        <v/>
+      </c>
+      <c r="N25" s="14">
+        <f>SUM(N23+N24)</f>
+        <v/>
+      </c>
+      <c r="O25" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30.45" customWidth="1" min="1" max="1"/>
+    <col width="14.45" customWidth="1" min="2" max="2"/>
+    <col width="20.45" customWidth="1" min="3" max="3"/>
+    <col width="18.45" customWidth="1" min="4" max="4"/>
+    <col width="18.45" customWidth="1" min="5" max="5"/>
+    <col width="18.45" customWidth="1" min="6" max="6"/>
+    <col width="18.45" customWidth="1" min="7" max="7"/>
+    <col width="18.45" customWidth="1" min="8" max="8"/>
+    <col width="18.45" customWidth="1" min="9" max="9"/>
+    <col width="18.45" customWidth="1" min="10" max="10"/>
+    <col width="18.45" customWidth="1" min="11" max="11"/>
+    <col width="18.45" customWidth="1" min="12" max="12"/>
+    <col width="18.45" customWidth="1" min="13" max="13"/>
+    <col width="26.45" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.4" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Washroom no</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Washroom (Gender)</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Vanity mirror</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Wash basin</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Washbasin Taps</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coat Hook </t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand Sanitizer </t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>Nappy Bin</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Water Heater </t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>Tissue Roll</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>Baby Seat</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand Tissue </t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="107.5" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="12" t="n"/>
+      <c r="N2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="20.15" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>GF - Tower 1</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="20.15" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="20.15" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>LGM - Tower 1</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="20.15" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="20.15" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>P1- Tower 1</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="20.15" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="20.15" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1- Tower 1 -PR Side </t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="20.15" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="20.15" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GF-Link Bridge -Food court</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="20.15" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="20.15" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> LGM-Link Bridge -Food court</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="20.15" customHeight="1">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="20.15" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> P1-Link Bridge -Food court</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="20.15" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="20.15" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GF -Tower 2 Food court </t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="20.15" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="20.15" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LGM -Tower 2 Food court </t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="20.15" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="20.15" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1-Tower 2 Food court </t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10">
+        <f>SUM(G3+G5+G7+G9+G11+G13+G15+G17)</f>
+        <v/>
+      </c>
+      <c r="H21" s="10">
+        <f>SUM(H3+H5+H7+H9+H11+H13+H15+H17)</f>
+        <v/>
+      </c>
+      <c r="I21" s="10">
+        <f>SUM(I3+I5+I7+I9+I11+I13+I15+I17)</f>
+        <v/>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="10">
+        <f>SUM(K3+K5+K7+K9+K11+K13+K15+K17)</f>
+        <v/>
+      </c>
+      <c r="L21" s="10">
+        <f>SUM(L3+L5+L7+L9+L11+L13+L15+L17)</f>
+        <v/>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="20.15" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="10">
+        <f>SUM(G4+G6+G8+G10+G12+G14+G16+G18)</f>
+        <v/>
+      </c>
+      <c r="H22" s="10">
+        <f>SUM(H4+H6+H8+H10+H12+H14+H16+H18)</f>
+        <v/>
+      </c>
+      <c r="I22" s="10">
+        <f>SUM(I4+I6+I8+I10+I12+I14+I16+I18)</f>
+        <v/>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="10">
+        <f>SUM(K4+K6+K8+K10+K12+K14+K16+K18)</f>
+        <v/>
+      </c>
+      <c r="L22" s="10">
+        <f>SUM(L4+L6+L8+L10+L12+L14+L16+L18)</f>
+        <v/>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="20.15" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D23" s="14">
+        <f>SUM(D3+D5+D7+D9+D11+D13+D15+D17+D19+D21)</f>
+        <v/>
+      </c>
+      <c r="E23" s="14">
+        <f>SUM(E3+E5+E7+E9+E11+E13+E15+E17+E19+E21)</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>SUM(F3+F5+F7+F9+F11+F13+F15+F17+F19+F21)</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>SUM(G3+G5+G7+G9+G11+G13+G15+G17+G19+G21)</f>
+        <v/>
+      </c>
+      <c r="H23" s="14">
+        <f>SUM(H3+H5+H7+H9+H11+H13+H15+H17+H19+H21)</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>SUM(I3+I5+I7+I9+I11+I13+I15+I17+I19+I21)</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>SUM(J3+J5+J7+J9+J11+J13+J15+J17+J19+J21)</f>
+        <v/>
+      </c>
+      <c r="K23" s="14">
+        <f>SUM(K3+K5+K7+K9+K11+K13+K15+K17+K19+K21)</f>
+        <v/>
+      </c>
+      <c r="L23" s="14">
+        <f>SUM(L3+L5+L7+L9+L11+L13+L15+L17+L19+L21)</f>
+        <v/>
+      </c>
+      <c r="M23" s="14">
+        <f>SUM(M3+M5+M7+M9+M11+M13+M15+M17+M19+M21)</f>
+        <v/>
+      </c>
+      <c r="N23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="20.15" customHeight="1">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D24" s="14">
+        <f>SUM(D4+D6+D8+D10+D12+D14+D16+D18+D20+D22)</f>
+        <v/>
+      </c>
+      <c r="E24" s="14">
+        <f>SUM(E4+E6+E8+E10+E12+E14+E16+E18+E20+E22)</f>
+        <v/>
+      </c>
+      <c r="F24" s="14">
+        <f>SUM(F4+F6+F8+F10+F12+F14+F16+F18+F20+F22)</f>
+        <v/>
+      </c>
+      <c r="G24" s="14">
+        <f>SUM(G4+G6+G8+G10+G12+G14+G16+G18+G20+G22)</f>
+        <v/>
+      </c>
+      <c r="H24" s="14">
+        <f>SUM(H4+H6+H8+H10+H12+H14+H16+H18+H20+H22)</f>
+        <v/>
+      </c>
+      <c r="I24" s="14">
+        <f>SUM(I4+I6+I8+I10+I12+I14+I16+I18+I20+I22)</f>
+        <v/>
+      </c>
+      <c r="J24" s="14">
+        <f>SUM(J4+J6+J8+J10+J12+J14+J16+J18+J20+J22)</f>
+        <v/>
+      </c>
+      <c r="K24" s="14">
+        <f>SUM(K4+K6+K8+K10+K12+K14+K16+K18+K20+K22)</f>
+        <v/>
+      </c>
+      <c r="L24" s="14">
+        <f>SUM(L4+L6+L8+L10+L12+L14+L16+L18+L20+L22)</f>
+        <v/>
+      </c>
+      <c r="M24" s="14">
+        <f>SUM(M4+M6+M8+M10+M12+M14+M16+M18+M20+M22)</f>
+        <v/>
+      </c>
+      <c r="N24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="20.15" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal </t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14">
+        <f>SUM(D23+D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="14">
+        <f>SUM(E23+E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="14">
+        <f>SUM(F23+F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="14">
+        <f>SUM(G23+G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="14">
+        <f>SUM(H23+H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="14">
+        <f>SUM(I23+I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="14">
+        <f>SUM(J23+J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="14">
+        <f>SUM(K23+K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="14">
+        <f>SUM(L23+L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="14">
+        <f>SUM(M23+M24)</f>
+        <v/>
+      </c>
+      <c r="N25" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30.45" customWidth="1" min="1" max="1"/>
+    <col width="14.45" customWidth="1" min="2" max="2"/>
+    <col width="20.45" customWidth="1" min="3" max="3"/>
+    <col width="18.45" customWidth="1" min="4" max="4"/>
+    <col width="18.45" customWidth="1" min="5" max="5"/>
+    <col width="18.45" customWidth="1" min="6" max="6"/>
+    <col width="18.45" customWidth="1" min="7" max="7"/>
+    <col width="18.45" customWidth="1" min="8" max="8"/>
+    <col width="18.45" customWidth="1" min="9" max="9"/>
+    <col width="18.45" customWidth="1" min="10" max="10"/>
+    <col width="18.45" customWidth="1" min="11" max="11"/>
+    <col width="18.45" customWidth="1" min="12" max="12"/>
+    <col width="26.45" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="37.4" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Washroom no</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Washroom (Gender)</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Soap</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Walls Mirror </t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marble Seat </t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Water Taps</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand Tissue </t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>Shoe Rack</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>Coat Box</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sofas </t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quiran Shelved </t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="107.5" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Photo Pls</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>Photo Pls</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="20.15" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1- Tower 1 -Prayer room </t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Male WR</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="20.15" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Female WR</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="20.15" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal </t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14">
+        <f>SUM(E3:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="14">
+        <f>SUM(F3:F4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="14">
+        <f>SUM(G3:G4)</f>
+        <v/>
+      </c>
+      <c r="H5" s="14">
+        <f>SUM(H3:H4)</f>
+        <v/>
+      </c>
+      <c r="I5" s="14">
+        <f>SUM(I3:I4)</f>
+        <v/>
+      </c>
+      <c r="J5" s="14">
+        <f>SUM(J3:J4)</f>
+        <v/>
+      </c>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14">
+        <f>SUM(L3:L4)</f>
+        <v/>
+      </c>
+      <c r="M5" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>